--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0069.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0069.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 12</t>
+          <t>Ngọn Cờ Chinh Phục: Chiến Dịch Trung 12</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 13</t>
+          <t>Ngọn Cờ Chinh Phục: Chiến Dịch Trung 13</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 14</t>
+          <t>Ngọn Cờ Chinh Phục: Chiến Dịch Trung 14</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 15</t>
+          <t>Ngọn Cờ Chinh Phục: Chiến Dịch Trung 15</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Major 16</t>
+          <t>Ngọn Cờ Chinh Phục: Cao 16</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 17</t>
+          <t>Ngọn Cờ Chinh Phục: Chiến Dịch Trung 17</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 18</t>
+          <t>Ngọn Cờ Chinh Phục: Chiến Dịch Trung 18</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 19</t>
+          <t>Ngọn Cờ Chinh Phục: Chiến Dịch Trung 19</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 2</t>
+          <t>Ngọn Cờ Chinh Phục: Cấp Trung 2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Major 20</t>
+          <t>Ngọn Cờ Chinh Phục: Đại Chiến Dịch 20</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Major 3</t>
+          <t>Ngọn Cờ Chinh Phục: Đại Chiến Dịch 3</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 4</t>
+          <t>Ngọn Cờ Chinh Phục: Cấp Trung 4</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 5</t>
+          <t>Ngọn Cờ Chinh Phục: Cấp Trung 5</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Major 6</t>
+          <t>Ngọn Cờ Chinh Phục: Đại Chiến Dịch 6</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 7</t>
+          <t>Ngọn Cờ Chinh Phục: Cấp Trung 7</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 8</t>
+          <t>Ngọn Cờ Chinh Phục: Cấp Trung 8</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Banner of Conquest: Medium 9</t>
+          <t>Ngọn Cờ Chinh Phục: Cấp Trung 9</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Temporary Activation</t>
+          <t>Kích Hoạt Tạm Thời</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Unactivated</t>
+          <t>Chưa kích hoạt</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Bộ đệm Khu vực Thử thách</t>
+          <t>Bổ trợ khu vực thử thách</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Tất cả-Resonator Attribute Buffss</t>
+          <t>Tăng Thuộc Tính Cho Tất Cả Resonator</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Activate</t>
+          <t>Kích Hoạt</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Temporary Activation</t>
+          <t>Kích Hoạt Tạm Thời</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Hết Hạn</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Cấp Độ Thử Thách</t>
+          <t>Cấp Độ Thử Nghiệm</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Explore City</t>
+          <t>Khám phá Thành phố</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Kích Hoạt Biểu Ngữ</t>
+          <t>Kích hoạt Banner</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Sự kiện kết thúc khi tất cả Banner được kích hoạt</t>
+          <t>Sự kiện kết thúc khi tất cả các Biểu Ngữ được kích hoạt.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Zone</t>
+          <t>Khu vực</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Tăng Cấp Độ Vinh Quang</t>
+          <t>Nâng Cấp Vinh Quang</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Nâng cấp Cấp độ GPA</t>
+          <t>Nâng Cấp GPA</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Kích hoạt Cấp Độ Vinh Quang</t>
+          <t>Đã Bật Cấp Độ Vinh Quang</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Kích hoạt Cấp Độ GPA</t>
+          <t>CẤP ĐỘ GPA ĐÃ KÍCH HOẠT</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Vô hiệu hóa Cấp Độ Vinh Quang</t>
+          <t>Đã Tắt Cấp Độ Vinh Quang</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Vô hiệu hóa Cấp Độ GPA</t>
+          <t>CẤP ĐỘ GPA ĐÃ VÔ HIỆU</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>[Chi tiết Thử thách]</t>
+          <t>[Chi Tiết Thử Thách]</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Theo dõi</t>
+          <t>Bản nhạc</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Phần thưởng Thử thách</t>
+          <t>Phần Thưởng Thử Thách</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Phần thưởng chưa nhận</t>
+          <t>Các phần thưởng chưa nhận</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Film Roll</t>
+          <t>Cuộn phim</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Watchlist Time Remaining</t>
+          <t>Thời gian Theo dõi Còn lại</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Tiệm cầm đồ Giấc mơ</t>
+          <t>Tiệm Cầm Đồ Giấc Mơ</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Cooldown Reduction</t>
+          <t>Giảm Thời gian hồi chiêu</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Dream Residue</t>
+          <t>Dư Vị Giấc Mơ</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Ally Recruitment I</t>
+          <t>Tuyển mộ Đồng minh I</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Dodge Heal</t>
+          <t>Hồi phục khi né</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Nâng Cấp Đội Hình I</t>
+          <t>Nâng Cấp Đội I</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Film Roll Capacity I</t>
+          <t>Dung lượng Cuộn phim I</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Dream Collection</t>
+          <t>Bộ Sưu Tập Mộng</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Crit. Rate Blessing</t>
+          <t>Phúc Lộc Bạo Kích</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Synergy Burst</t>
+          <t>Cộng Hưởng Bùng Nổ</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Ally Recruitment II</t>
+          <t>Tuyển mộ Đồng minh II</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>DMG Reduction</t>
+          <t>Giảm Sát Thương</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Recruitment Discount</t>
+          <t>Giảm giá chiêu mộ</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Ally Recruitment III</t>
+          <t>Tuyển mộ Đồng minh III</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Film Roll Capacity II</t>
+          <t>Dung lượng Cuộn phim II</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Nâng Cấp Đội Hình II</t>
+          <t>Nâng Cấp Đội II</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>ATK Up I</t>
+          <t>Tăng ATK I</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>ATK Up II</t>
+          <t>Tăng ATK II</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>ATK Up III</t>
+          <t>Tăng ATK III</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>ATK Up IV</t>
+          <t>Tăng ATK IV</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>ATK Up V</t>
+          <t>Tăng ATK V</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>ATK Up VI</t>
+          <t>Tăng ATK VI</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>HP Up I</t>
+          <t>Tăng HP I</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>HP Up II</t>
+          <t>Tăng HP II</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>HP Up IV</t>
+          <t>Tăng HP IV</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>HP Up V</t>
+          <t>Tăng HP V</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Thử thách Kịch bản</t>
+          <t>Thử Thách Kịch Bản</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Thử thách Mối Liên Kết</t>
+          <t>Thử Thách Gắn Kết</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Thử thách Giai Đoạn</t>
+          <t>Thử Thách Giai Đoạn</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Thử thách Tiếp Nối</t>
+          <t>Thử Thách Theo Dõi</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Tất cả Bonds</t>
+          <t>Tất Cả Mối Duyên</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Synergy Burst khả dụng</t>
+          <t>Cộng Hưởng Bùng Nổ sẵn sàng</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Hide Bond</t>
+          <t>Ẩn Liên Kết</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Xếp hạng Sao tăng</t>
+          <t>Xếp hạng Sao tăng lên</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Cấp Độ Gắn Kết tăng</t>
+          <t>Cấp Độ Gắn Kết tăng lên</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Hoàn thành Phim "Anh Hùng Biến Hình: Chiến Binh Lửa"</t>
+          <t>Hoàn thành Bộ Phim "Anh Hùng Biến Hình: Kỵ Sĩ Lửa"</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Cấp Độ Đội</t>
+          <t>Cấp Đội</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>Con đường</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Common Battle</t>
+          <t>Trận Chiến Thường</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Elite Battle</t>
+          <t>Đấu Trường Tinh Anh</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Strange Gateway</t>
+          <t>Cánh Cổng Bí Ẩn</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Boss Battle</t>
+          <t>Trận Chiến Trùm</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Phần thưởng Mảnh</t>
+          <t>Phần thưởng Mảnh vỡ</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Unknown Metaphors</t>
+          <t>Ẩn dụ vô danh</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Main Story: Meeting Allies</t>
+          <t>Cốt Truyện Chính: Gặp Gỡ Đồng Minh</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Chương Chính: Lark tại Nhà Ga</t>
+          <t>Cốt Truyện Chính: Lark Tại Nhà Ga</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Chương Chính: Cái Giá của Sức Mạnh</t>
+          <t>Cốt Truyện Chính: Cái Giá Của Sức Mạnh</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Main Story: Flame Ranger</t>
+          <t>Cốt Truyện Chính: Kỵ Sĩ Lửa</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Chương Chính: Nhân Danh Anh Hùng</t>
+          <t>Cốt Truyện Chính: Nhân Danh Anh Hùng</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Interlude: The Starflower Brooch</t>
+          <t>Chương xen: Trâm hoa sao</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Interlude: The Patient's Fate</t>
+          <t>Chương xen: Số phận của bệnh nhân</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Encounter: Central Hospital</t>
+          <t>Đối đầu: Bệnh Viện Trung Tâm</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Interlude: The Enigmatic Artist</t>
+          <t>Chương xen: Nghệ sĩ bí ẩn</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Interlude: Sports Cửa hàng</t>
+          <t>Chương xen: Cửa hàng thể thao</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Encounter: Claw Machine</t>
+          <t>Đối đầu: Máy Bắt Thú Càng</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Chặng Phụ: Điều Tra Bí Mật</t>
+          <t>Khúc Tạm Ngừng: Điều Tra Viên Mật</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Interlude: The Cancelled Performance</t>
+          <t>Chương xen: Buổi biểu diễn bị hủy bỏ</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Encounter: The Truth Bench</t>
+          <t>Gặp Gỡ: Ghế Công Lý</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Tai Nạn trên phim trường</t>
+          <t>Đối đầu: Sự Cố Trên Trường Quay</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Encounter: False Advertising</t>
+          <t>Gặp Gỡ: Quảng Cáo Lừa Dối</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Encounter: Sobering Behavior</t>
+          <t>Gặp Gỡ: Hành Vi Tỉnh Táo</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Encounter: The Weeping Band</t>
+          <t>Gặp Gỡ: Ban Nhạc Than Khóc</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Main Story: Inn</t>
+          <t>Cốt Truyện Chính: Quán Trọ</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Main Story: Temple</t>
+          <t>Cốt Truyện Chính: Đền Thờ</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Main Story: Reunion</t>
+          <t>Cốt Truyện Chính: Đoàn Tụ</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Main Story: Loong Chamber</t>
+          <t>Cốt Truyện Chính: Đại Sảnh Loong</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Main Story: Execution</t>
+          <t>Cốt Truyện Chính: Thi Hành Án</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Chặng Phụ: Làn Khói Mong Manh</t>
+          <t>Chương xen: Làn khói mong manh</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Interlude: Mirage</t>
+          <t>Chương xen: Ảo Ảnh</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Interlude: Jade</t>
+          <t>Chương xen: Jade</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Interlude: Monk</t>
+          <t>Chương xen: Nhà Sư</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Interlude: Codeword</t>
+          <t>Khúc Tạm Ngừng: Mật Danh</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Interlude: Leisure</t>
+          <t>Chương xen: Nhàn Hạ</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Encounter: Dreamy Spring</t>
+          <t>Gặp Gỡ: Suối Mộng Xuân</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Encounter: White Wolf</t>
+          <t>Gặp gỡ: Sói Trắng</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Encounter: Glacier</t>
+          <t>Gặp Gỡ: Sông Băng</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Encounter: Last Desire</t>
+          <t>Gặp gỡ: Khát Vọng Cuối Cùng</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Encounter: Freedom</t>
+          <t>Gặp Gỡ: Tự Do</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Encounter: Secret Market</t>
+          <t>Gặp gỡ: Chợ Đen</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Main Story: Black Vacation</t>
+          <t>Câu Chuyện Chính: Kỳ Nghỉ Đen Tối</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Chương Chính: Hương Thơm trong Hang Động</t>
+          <t>Câu Chuyện Chính: Hương Thơm Trong Hang Động</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Main Story: Information Broker</t>
+          <t>Cốt Truyện Chính: Tay Môi Giới Thông Tin</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Main Story: Hệ thống Hub</t>
+          <t>Cốt Truyện Chính: Trung Tâm Hệ Thống</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Chương Chính: Bờ Biển Bị Bao Phủ Bí Ẩn</t>
+          <t>Cốt Truyện Chính: Bờ Biển Bí Ẩn</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Main Story: The Eternal Watch</t>
+          <t>Cốt Truyện Chính: Người Canh Gác Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Chương Chính: Những Linh Hồn Ngoài Hố Đen</t>
+          <t>Cốt Truyện Chính: Những Linh Hồn Vượt Thời Không</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Interlude: Red-haired Analyzer</t>
+          <t>Chương xen: Nhà Phân Tích Tóc Đỏ</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Chặng Phụ: Người Đưa Thư Màu Hồng</t>
+          <t>Chương xen: Người Đưa Tin Áo Hồng</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Interlude: Wooly Warrior</t>
+          <t>Chương xen: Chiến binh lông lá</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Chặng Phụ: Thủ Lĩnh Lính Đánh Thuê</t>
+          <t>Chương xen: Thủ Lĩnh Lính Đánh Thuê</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Chặng Phụ: Điều Tra Viên Chính</t>
+          <t>Chương xen: Điều Tra Viên Trưởng</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Encounter: Secret Campsite I</t>
+          <t>Gặp gỡ: Điểm Cắm Trại Bí Mật I</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Encounter: Secret Campsite II</t>
+          <t>Gặp gỡ: Điểm Cắm Trại Bí Mật II</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Encounter: Siege</t>
+          <t>Gặp gỡ: Bao Vây</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Encounter: Sentry's Creed</t>
+          <t>Gặp gỡ: Lời Thề Của Lính Canh</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Nơi Nghỉ Ngơi Bình Yên I</t>
+          <t>Gặp gỡ: Nơi Nghỉ Ngơi I</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Nơi Nghỉ Ngơi Bình Yên II</t>
+          <t>Gặp gỡ: Nơi Nghỉ Ngơi II</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Nơi Nghỉ Ngơi Bình Yên III</t>
+          <t>Gặp gỡ: Nơi Nghỉ Ngơi III</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Encounter: Solaris Retail I</t>
+          <t>Gặp Gỡ: Khu Thương Mại Solaris I</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Encounter: Solaris Retail II</t>
+          <t>Gặp Gỡ: Khu Thương Mại Solaris II</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Encounter: Solaris Retail III</t>
+          <t>Gặp Gỡ: Khu Thương Mại Solaris III</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Encounter: The Cats Call I</t>
+          <t>Gặp Gỡ: Tiếng Gọi Của Mèo I</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Encounter: The Cats Call II</t>
+          <t>Gặp Gỡ: Tiếng Gọi Của Mèo II</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Encounter: Strange Telephone Booth I</t>
+          <t>Gặp Gỡ: Buồng Điện Thoại Kỳ Lạ I</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Encounter: Strange Telephone Booth II</t>
+          <t>Gặp Gỡ: Buồng Điện Thoại Kỳ Lạ II</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Chuyến Đi Trên Chuyến Tàu Bị Bỏ Hoang I</t>
+          <t>Gặp gỡ: Chuyến Tàu Bỏ Hoang I</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Chuyến Tàu Bị Bỏ Hoang II</t>
+          <t>Gặp gỡ: Chuyến Tàu Bỏ Hoang II</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Giai Điệu Từ Bãi Rác I</t>
+          <t>Gặp gỡ: Giai điệu từ Bãi Rác I</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Giai Điệu Từ Bãi Rác II</t>
+          <t>Gặp gỡ: Giai điệu từ Bãi Rác II</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Giai Điệu Từ Bãi Rác III</t>
+          <t>Gặp gỡ: Giai điệu từ Bãi Rác III</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Màu Sắc Từ Trái Tim I</t>
+          <t>Đối đầu: Sắc Màu Ngoài Trái Tim I</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Màu Sắc Từ Trái Tim II</t>
+          <t>Gặp Gỡ: Màu Sắc Ngoài Trái Tim II</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Màu Sắc Từ Trái Tim III</t>
+          <t>Gặp Gỡ: Màu Sắc Ngoài Trái Tim III</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Encounter: Forsaken Package I</t>
+          <t>Gặp Gỡ: Gói Hàng Bị Lãng Quên I</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Encounter: Forsaken Package II</t>
+          <t>Gặp Gỡ: Gói Hàng Bị Lãng Quên II</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Encounter: Forsaken Package III</t>
+          <t>Gặp Gỡ: Gói Hàng Bị Lãng Quên III</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Encounter: Violet Vine Path I</t>
+          <t>Gặp gỡ: Con Đường Hoa Tím I</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Encounter: Violet Vine Path II</t>
+          <t>Gặp gỡ: Con Đường Hoa Tím II</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Cây Cô Đơn Nơi Góc Hoang Vắng I</t>
+          <t>Gặp gỡ: Cây Cô Đơn Nơi Góc Hoang Tàn I</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Cây Cô Đơn Nơi Góc Hoang Vắng II</t>
+          <t>Gặp gỡ: Cây Cô Đơn Nơi Góc Hoang Tàn II</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Encounter: Old Clay Pots I</t>
+          <t>Gặp gỡ: Những Chiếc Bình Cũ I</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Encounter: Old Clay Pots II</t>
+          <t>Gặp gỡ: Những Chiếc Bình Cũ II</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Encounter: Mine I</t>
+          <t>Gặp gỡ: Mỏ Khoáng I</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Encounter: Mine II</t>
+          <t>Gặp gỡ: Mỏ Khoáng II</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Thắp Sáng Vầng Trăng I</t>
+          <t>Gặp gỡ: Thắp Sáng Vầng Trăng I</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Thắp Sáng Vầng Trăng II</t>
+          <t>Gặp gỡ: Thắp Sáng Vầng Trăng II</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Encounter: Weightless Ruins I</t>
+          <t>Gặp gỡ: Tàn Tích Không Trọng Lực I</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Encounter: Weightless Ruins II</t>
+          <t>Gặp gỡ: Tàn Tích Không Trọng Lực II</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Tiếng Gọi Dưới Đáy Biển I</t>
+          <t>Gặp gỡ: Tiếng Gọi Từ Đáy Biển I</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Tiếng Gọi Dưới Đáy Biển I</t>
+          <t>Gặp gỡ: Tiếng Gọi Từ Đáy Biển I</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Interlude: The Aetherfins</t>
+          <t>Chương xen: Đội Aetherfin</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Urban Encounters</t>
+          <t>Gặp Gỡ Đô Thị</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Dấu Chân Trong Tuyết</t>
+          <t>Dấu chân trên tuyết</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Dạo Chơi Trên Bãi Biển</t>
+          <t>Dạo Bờ Biển</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Chương Chính: Trở Về Từ Bóng Đêm</t>
+          <t>Cốt Truyện Chính: Trở Về Từ Bóng Đêm</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Chương Chính: Rạp Xiếc Của Các Học Giả</t>
+          <t>Câu Chuyện Chính: Rạp Xiếc Của Các Bậc Thông Thái</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Chương Chính: Viên Chức Giao Thức</t>
+          <t>Cốt Truyện Chính: Sĩ Quan Giao Thức</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Chương Chính: Món Nợ Đã Được Thanh Toán</t>
+          <t>Cốt Truyện Chính: Mối Nợ Đã Đền</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Main Story: The High Adjudicator</t>
+          <t>Cốt Truyện Chính: Vị Thẩm Phán Tối Cao</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Interlude: Sea Pianist</t>
+          <t>Chương xen: Nghệ Sĩ Piano Biển</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Interlude: Current President</t>
+          <t>Chương xen: Tổng Thống Hiện Tại</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Chương Phụ: Ngọc Opal và Mắt Mèo</t>
+          <t>Chương xen: Opal và Mắt Mèo</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Encounter: Gondola Market I</t>
+          <t>Gặp Gỡ: Chợ Gondola I</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Encounter: Gondola Market II</t>
+          <t>Gặp gỡ: Chợ Gondola II</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Encounter: Fallen Knights</t>
+          <t>Gặp Gỡ: Những Hiệp Sĩ Sa Ngã</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Encounter: Golden Ridge</t>
+          <t>Gặp Gỡ: Dãy Vàng</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Encounter: Auction I</t>
+          <t>Đối đầu: Phiên Đấu Giá I</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Encounter: Auction II</t>
+          <t>Đối đầu: Phiên Đấu Giá II</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Những Cuộc Gặp Gỡ Ở Thành Phố Nước</t>
+          <t>Những Cuộc Gặp Gỡ Tại Thành Phố Nước</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Encounter: Auction III</t>
+          <t>Đối đầu: Phiên Đấu Giá III</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Main Story: Crime Thông báo</t>
+          <t>Câu Chuyện Chính: Thông Báo Tội Ác</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Main Story: The First Victim</t>
+          <t>Cốt Truyện Chính: Nạn Nhân Đầu Tiên</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Main Story: Investigation</t>
+          <t>Cốt Truyện Chính: Điều Tra</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Main Story: Malice</t>
+          <t>Cốt Truyện Chính: Ác Ý</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Chương Chính: Mâu Thuẫn và Nghi Ngờ</t>
+          <t>Câu Chuyện Chính: Mâu Thuẫn Và Nghi Ngờ</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Main Story: Final Clue</t>
+          <t>Cốt Truyện Chính: Manh Mối Cuối Cùng</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Main Story: Debate Time</t>
+          <t>Cốt Truyện Chính: Giờ Tranh Luận</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Main Story: The Slumbering Seabed</t>
+          <t>Cốt Truyện Chính: Đại Dương Ngủ Quên</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Main Story: The Somnoire Breeze</t>
+          <t>Cốt Truyện Chính: Gió Ngủ Đông</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Chương Chính: Cái Nôi Vĩnh Hằng</t>
+          <t>Câu Chuyện Chính: Cái Nôi Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Main Story: The Long Featurette</t>
+          <t>Cốt Truyện Chính: Đoạn Phim Dài</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Món Quà Từ Bầu Trời</t>
+          <t>Đối đầu: Món Quà Từ Bầu Trời</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Ý Nghĩa Của Lời Nói</t>
+          <t>Gặp gỡ: Ý Nghĩa Của Lời Nói</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Encounter: Blind Star</t>
+          <t>Đối đầu: Ngôi Sao Mù</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Encounter: A Tumbleyak Sitting Still</t>
+          <t>Đối đầu: Tumbleyak Bất Động</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Gõ Cửa</t>
+          <t>Gặp gỡ: Gõ Cửa</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Encounter: Wishing Machine</t>
+          <t>Gặp gỡ: Cỗ Máy Điều Ước</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Encounter: Somnoire Express</t>
+          <t>Gặp Gỡ: Tàu Tốc Hành Somnoire</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Encounter: Watchers</t>
+          <t>Gặp gỡ: Những Kẻ Theo Dõi</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Thành Phố Phạm Tội</t>
+          <t>Đối đầu: Thành Phố Phạm Tội</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Lý Do Để Bảo Vệ</t>
+          <t>Gặp Gỡ: Lý Do Bảo Vệ</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Anonymous Poster</t>
+          <t>Bài đăng ẩn danh</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Gặp Gỡ: Nơi Nghỉ Ngơi An Toàn IV</t>
+          <t>Gặp gỡ: Nơi Nghỉ Ngơi IV</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Main Story: Final Case</t>
+          <t>Cốt Truyện Chính: Vụ Án Cuối Cùng</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Câu Chuyện Chính: Khúc Dạo Đầu Carnevale</t>
+          <t>Cốt Truyện Chính: Khúc Dạo Đầu Carnevale</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Calm Female Giọng nói [News Broadcast]</t>
+          <t>Giọng nữ bình tĩnh [Tin tức phát thanh]</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Người Đàn Ông Có Tai Nghe [Phóng Viên]</t>
+          <t>Người Đàn Ông Đeo Tai Nghe [Phóng Viên]</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Người Đàn Ông Phấn Khích [Khán Giả]</t>
+          <t>Người đàn ông háo hức [Khán giả]</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Người Đàn Ông Có Tai Nghe [Phóng Viên]</t>
+          <t>Người Đàn Ông Đeo Tai Nghe [Phóng Viên]</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Hot-headed Teen [Onlooker]</t>
+          <t>Thiếu Niên Nóng Tính [Người Quanh]</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Những Đứa Trẻ Trong Công Viên [Khán Giả]</t>
+          <t>Trẻ Em Trong Công Viên [Người Quanh]</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Heat Seeker [Flame Ranger]</t>
+          <t>Thợ Săn Lửa [Pháo Thủ Hỏa Diệm]</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Vehicle Siren [Emergency Services]</t>
+          <t>Còi Báo Động [Dịch Vụ Khẩn Cấp]</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Racing Ambulance [Emergency Services]</t>
+          <t>Xe Cứu Thương Tốc Độ [Dịch Vụ Cấp Cứu]</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Loud Speakers [Public Service Announcement]</t>
+          <t>Loa Công Cộng [Thông Báo Công Cộng]</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Đồng Minh Công Lý [Flame Ranger]</t>
+          <t>Đồng minh Công lý [Blaze Ranger]</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Lạnh Lùng [Giáo Sư You'tan]</t>
+          <t>Nhà Nghiên Cứu Băng Giá [Giáo Sư You'tan]</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Serious Female Giọng nói [News Broadcast]</t>
+          <t>Giọng Nữ Nghiêm Túc [Tin Tức Phát Sóng]</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Người Đàn Ông Có Tai Nghe [Phóng Viên]</t>
+          <t>Người Đàn Ông Đeo Tai Nghe [Phóng Viên]</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Mọi người Together</t>
+          <t>Cùng nhau</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Nhân Viên Tiếp Tân Bận Rộn [Quầy Lễ Tân Bệnh Viện]</t>
+          <t>Lễ tân bận rộn [Quầy lễ tân bệnh viện]</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Cô Gái Đội Mũ Beret [D]</t>
+          <t>Cô gái đội mũ nồi [D]</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Anxious Artist [Popular Illustrator]</t>
+          <t>Họa Sĩ Lo Âu [Họa Sĩ Nổi Tiếng]</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Kẻ Phá Vỡ Giấc Mơ Tuổi Thơ [Máy Bắt Thú]</t>
+          <t>Kẻ Nghiền Nát Giấc Mơ Tuổi Thơ [Máy Bắt Đồ]</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Khách Du Lịch Với Trang Phục Sư Tử [Ngôi Sao Nổi Tiếng]</t>
+          <t>Du khách hóa sư tử [Ngôi sao nổi tiếng]</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Người Đàn Ông Có Máy Ảnh [Nhân Viên Quay Phim]</t>
+          <t>Người Đàn Ông Cầm Máy Quay [Nhân Viên Quay Phim]</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Người Tuyển Dụng Anh Hùng [Đạo Diễn Nổi Tiếng]</t>
+          <t>Nhà Tuyển Dụng Anh Hùng [Đạo diễn Nổi Tiếng]</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Furious Lead Singer [Lighting Technician]</t>
+          <t>Ca Sĩ Chính Cuồng Nộ [Kỹ Thuật Viên Ánh Sáng]</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Cô Gái Với Đàn Guitar [D]</t>
+          <t>Cô Gái Và Chiếc Đàn Guitar [D]</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Người Chơi Trống Trong Đồng Phục [Bậc Thầy Hóa Trang]</t>
+          <t>Drummer trong Đồng Phục [Bậc Thầy Trang Điểm]</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Đánh bại Những Cơn Ác Mộng</t>
+          <t>Hạ gục lũ Ác Mộng.</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Cùng nhau lên đường</t>
+          <t>Cùng nhau tiến bước</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Cùng nhau lên đường</t>
+          <t>Cùng nhau tiến bước</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Trở thành Anh Hùng</t>
+          <t>Hãy trở thành anh hùng</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Yinlin đã gia nhập đội của bạn</t>
+          <t>Yinlin đã gia nhập đội của cậu.</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Cô Gái Khoác Áo Choàng [Thời Gian Đông Cứng]</t>
+          <t>Cô Gái Áo Choàng [Thời Gian Đông Cứng]</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Defeated Mercenary [Scarred Face]</t>
+          <t>Đánh bại Lính đánh thuê [Sẹo Trên Mặt]</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Opportunistic Bandit [Broken Nose]</t>
+          <t>Kẻ Cướp Cơ Hội [Mũi Gãy]</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Young Bandit [Black Mask]</t>
+          <t>Kẻ Cướp Nhí [Mặt Nạ Đen]</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Nữ Kiếm Sĩ Asura [Kẻ Siêu Việt Nỗi Đau]</t>
+          <t>Kiếm Khách Asura [Kẻ Siêu Việt Nỗi Đau]</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Người Phụ Nữ Cầm Ô Mỉm Cười [Lửa Vĩnh Cửu]</t>
+          <t>Cô Gái Cười Dưới Ô [Ngọn Lửa Vĩnh Hằng]</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Cô Gái Khoác Áo Choàng [Sự Tỉnh Thức Của Mùa Xuân]</t>
+          <t>Cô Gái Áo Choàng [Sự Thức Tỉnh Của Mùa Xuân]</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Người Đàn Ông Hào Hứng [Người Bán Chè Trôi Nước]</t>
+          <t>Người đàn ông phấn khích [Bán chè Thủy Tụ]</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Cô Gái Tóc Bạc [Sự Lui Tới Của Mùa Đông]</t>
+          <t>Cô Gái Tóc Bạc [Nơi Trú Đông]</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Crying Baby [Past Reverberation]</t>
+          <t>Đứa Trẻ Khóc Lóc [Dư Âm Quá Khứ]</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Mournful Mother [Past Reverberation]</t>
+          <t>Người Mẹ Đau Buồn [Dư Âm Quá Khứ]</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Aloof Father [Past Reverberation]</t>
+          <t>Người Cha Lạnh Lùng [Dư Âm Quá Khứ]</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Cô Bé Cầm Ô [Dư Âm Quá Khứ]</t>
+          <t>Cô Bé Ô Dù [Dư Âm Quá Khứ]</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Cô Gái Khoác Áo Choàng [Dư Âm Quá Khứ]</t>
+          <t>Cô Gái Áo Choàng [Dư Âm Quá Khứ]</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Cô Gái Đeo Vòng Ngọc [Bóng Đỏ Thẫm]</t>
+          <t>Cô Gái Với Mảnh Jade [Sắc Đỏ Thẫm]</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Lão Đạo Sĩ Nghèo Khó [Kẻ Đam Mê Giản Đơn]</t>
+          <t>Đạo Sĩ Nghèo [Kẻ Ôm Ấp Sự Giản Đơn]</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Cô Gái Lém Lỉnh [Chuyên Gia Đánh Giá]</t>
+          <t>Cô Gái Lưỡi Dao [Thẩm Định Viên Tài Ba]</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Thương Nhân Đồ Cổ [Nhà Sưu Tập Kì Cựu]</t>
+          <t>Thương Nhân Đồ Cổ [Nhà Sưu Tầm Kì Cựu]</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Feeble Henchman [Merchant's Lackey]</t>
+          <t>Tay sai yếu ớt [Tay chân của thương nhân]</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Du Khách Lười Biếng [Đóa Hoa Vết Cắt]</t>
+          <t>Du Khách Lười Biếng [Bông Hoa Chém Gió]</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Vanishing Frequency [Dying Echo]</t>
+          <t>Tần Số Tan Biến [Tiếng Vọng Hấp Hối]</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hero Admirer [Lighting Technician]</t>
+          <t>Người Hâm Mộ Anh Hùng [Kỹ Thuật Viên Ánh Sáng]</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>War Enthusiast [Camera Operator]</t>
+          <t>Người Yêu Chiến Tranh [Nhân viên Quay phim]</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Hedonic Seeker [Makeup Designer]</t>
+          <t>Kẻ Tìm Kiếm Sung Sướng [Nhà Thiết Kế Trang Điểm]</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Quiet Observer [Film Editor]</t>
+          <t>Người Quan Sát Lặng Lẽ [Biên Tập Phim]</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Cautious Speaker [Film Producer]</t>
+          <t>Nhà Sản Xuất Phim Thận Trọng</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Dying Mercenary [Black Mask]</t>
+          <t>Lính đánh thuê hấp hối [Mặt nạ Đen]</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>The Unbound [Đôi Cánh Tự Do]</t>
+          <t>Đôi Cánh Tự Do [Không Gông Cùm]</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Nâng cấp Jinhsi</t>
+          <t>Nâng Cấp Jinhsi</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Chọn một Metaphor</t>
+          <t>Chọn Ẩn Dụ</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Sanhua đã tham gia đội của bạn</t>
+          <t>Sanhua đã gia nhập đội của bạn</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Changli đã tham gia đội của bạn</t>
+          <t>Changli đã gia nhập đội của bạn</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Nâng cấp Sanhua</t>
+          <t>Nâng Cấp Sanhua</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Danjin đã tham gia đội của bạn</t>
+          <t>Danjin đã gia nhập đội của bạn</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Tiêu hao 300 Mảnh Giấc Mơ để nhận 1 Metaphor</t>
+          <t>Dùng 300 Mảnh Giấc Mơ để nhận 1 Ẩn Dụ</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Jianxin đã tham gia đội của bạn</t>
+          <t>Jianxin đã gia nhập đội của cậu</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Youhu đã tham gia đội của bạn</t>
+          <t>Youhu đã gia nhập đội của cậu.</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Bedtime Stories</t>
+          <t>Những Câu Chuyện Trước Khi Ngủ</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Taoqi đã tham gia đội của bạn</t>
+          <t>Taoqi đã gia nhập đội của bạn</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Nhận 200 Mảnh Giấc mơ</t>
+          <t>Thu thập 200 Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Tiêu hao 12 Cuộn Phim để nhận 200 Mảnh Giấc Mơ</t>
+          <t>Dùng 12 Cuộn Phim để nhận 200 Mảnh Giấc Mơ.</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Dorothy [Pure Illusion]</t>
+          <t>Dorothy [Ảo Ảnh Thuần Khiết]</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Abandoned Shelf [Solaris Retail]</t>
+          <t>Kệ Hàng Bị Bỏ Rơi [Solaris Retail]</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Strange White Cat [Ivory Gatekeeper]</t>
+          <t>Con mèo trắng kỳ lạ [Người gác cổng Ngà]</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Taciturn Black Cat [Ebony Gatekeeper]</t>
+          <t>Mèo Đen Lầm Lì [Người Gác Cổng Hắc Ám]</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Strange Telephone Booth [Last Echo]</t>
+          <t>Buồng điện thoại kỳ lạ [Echo cuối cùng]</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Stored Giọng nói [Film Producer]</t>
+          <t>Ghi Âm Lưu Trữ [Nhà Sản Xuất Phim]</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Late-Night Tavern Commuter [Stunt Double]</t>
+          <t>Lữ Khách Quán Rượu Đêm [Diễn Viên Đóng Thế]</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Well-Dressed Steward [Film Editor]</t>
+          <t>Quản Gia Ăn Mặc Chỉnh Tề [Biên Tập Viên Phim]</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Nhân Chứng Hành Trình [Nhiếp Ảnh Gia]</t>
+          <t>Nhật ký hành trình [Người quay phim]</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Chuột Nói Chuyện [Đạo Diễn Nổi Tiếng]</t>
+          <t>Chuột Cống Nói [Đạo diễn Nổi tiếng]</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Whispering Painting [Dream Mortician]</t>
+          <t>Bức Tranh Thì Thầm [Người Chôn Giấc Mộng]</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Dust-Covered Letter [Humanities Enthusiast]</t>
+          <t>Lá Thư Phủ Bụi [Người Yêu Nhân Văn]</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Withered Tree [Humanities Enthusiast]</t>
+          <t>Cây Khô Héo [Người Đam Mê Nhân Văn]</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Newborn Tree [Humanities Enthusiast]</t>
+          <t>Cây Mới Nảy Mầm [Người Đam Mê Nhân Văn]</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Âm Thanh Lạc Trong Ký Ức [Tiếng Nói của Somnoire]</t>
+          <t>Âm thanh thất lạc trong Ký ức [Giọng của Somnoire]</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Dùng 100 Mảnh Giấc Mơ để khôi phục 12 Cuộn Phim</t>
+          <t>Dùng 100 Mảnh Giấc Mơ để đổi lấy 12 Cuộn Phim</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Tiêu hao 200 Mảnh Giấc Mơ để nhận 1 Metaphor ngẫu nhiên</t>
+          <t>Dùng 200 Mảnh Giấc Mơ để nhận ngẫu nhiên 1 Ẩn Dụ</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Thắng một trận khó để nhận 100 Mảnh Giấc Mơ và mở Cửa Hàng Tuyển Dụng Nâng Cao</t>
+          <t>Chiến thắng trận chiến khó để nhận 100 Mảnh Giấc Mơ và mở cửa hàng Tuyển Dụng Cao Cấp</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Mở Cửa Hàng Tuyển Dụng tặng Mảnh Giấc Mơ ngẫu nhiên</t>
+          <t>Mở Cửa Hàng Tuyển Dụng tặng mảnh Giấc Mơ ngẫu nhiên</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Nhận 160 Mảnh Giấc mơ</t>
+          <t>Thu thập 160 Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Mở Cửa Hàng Tuyển Dụng chỉ chứa Resonator Súng Ngắn hoặc Kiếm</t>
+          <t>Mở Cửa Hàng Tuyển Mộ chỉ có Resonator Pistol hoặc Kiếm đơn</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Mở Cửa Hàng Tuyển Dụng chỉ chứa Resonator Broadblade, Gauntlets hoặc Rectifier</t>
+          <t>Mở Cửa Hàng Tuyển Mộ chỉ có Resonator Đại kiếm, Găng tay hoặc Pháp khí</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Tiêu hao 4 Cuộn Phim để trả lời</t>
+          <t>Dùng 4 Cuộn Phim để trả lời</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Nhận 160 Mảnh Giấc mơ</t>
+          <t>Thu thập 160 Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Dùng 160 Mảnh Giấc Mơ để mở Cửa Hàng Tăng Cường Resonator</t>
+          <t>Dùng 160 Mảnh Giấc Mơ để mở Cửa Hàng Tăng Cường Resonator.</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Vision Range +1</t>
+          <t>Tầm Nhìn +1</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Vision Range +1</t>
+          <t>Tầm Nhìn +1</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Nhận 200 Mảnh Giấc mơ</t>
+          <t>Thu thập 200 Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Nhận thêm 20% Cuộn Phim</t>
+          <t>Nhận thêm 20% cuộn phim</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Nhận 100 Mảnh Giấc mơ</t>
+          <t>Thu thập 100 Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Thắng trận khó để mở Cửa Hàng Tuyển Dụng Cao Cấp</t>
+          <t>Chiến thắng trận chiến khó để mở cửa hàng Tuyển Dụng Cao Cấp</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Nhận 100 hoặc 200 Mảnh Giấc Mơ</t>
+          <t>Thu thập 100 hoặc 200 Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Dùng 4 Cuộn Phim để tuyển dụng Resonator mới</t>
+          <t>Dùng 4 Cuộn Phim để tuyển một Resonator mới</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Nhận thêm 20% Cuộn Phim</t>
+          <t>Nhận thêm 20% cuộn phim</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Thắng trận để nhận 12 Cuộn Phim</t>
+          <t>Chiến thắng trận đấu để nhận 12 Cuộn Phim</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>4 Sự Kiện Chiến Đấu gần đây</t>
+          <t>4 Sự Kiện Chiến Đấu Gần Đây</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>2 Sự Kiện Chiến Đấu gần đây</t>
+          <t>2 Sự Kiện Chiến Đấu Gần Đây</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Mở Cửa Hàng Tuyển Dụng Đặc Biệt (Resonator có Mối Liên Kết hiếm)</t>
+          <t>Mở Cửa Hàng Tuyển Mộ Đặc Biệt (Resonator có Mối Liên Kết hiếm)</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Mở Cửa Hàng Tuyển Dụng Đặc Biệt (Resonator Hỗ Trợ)</t>
+          <t>Mở Cửa Hàng Tuyển Mộ Đặc Biệt (Resonator Hỗ Trợ)</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Cùng nhau lên đường</t>
+          <t>Cùng nhau tiến bước</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Dùng 160 Mảnh Giấc Mơ để mở Cửa Hàng Tuyển Dụng Đặc Biệt</t>
+          <t>Dùng 160 Mảnh Giấc Mơ để mở Cửa Hàng Tuyển Dụng Đặc Biệt.</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Blooming Camellia [Crimson Shadow]</t>
+          <t>Hồng Nở [Bóng Đỏ Thẫm]</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Tethys [Torrent Prescient]</t>
+          <t>Tethys [Dự Báo Hồng Thủy]</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Blue Butterfly [Astral Prescient]</t>
+          <t>Bươm Bướm Xanh [Thiên Cơ Tiên Tri]</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Wooly Warrior [Fleece Prescient]</t>
+          <t>Chiến Binh Lông Xù [Lông Tiên Tri]</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Red Dragon [Red-haired Analyzer]</t>
+          <t>Red Dragon [Bộ Phân Tích Tóc Đỏ]</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Siren Alarm</t>
+          <t>Báo động Siran</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Chuột Hamster Lấp Lánh [Người Đưa Tin Màu Hồng]</t>
+          <t>Chú Hamster Lấp Lánh [Phu Trạm Màu Hồng]</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Hào Quang Đáng Sợ [Thủ Lĩnh Lính Đánh Thuê]</t>
+          <t>Hào Khí Bất Khuất [Thủ Lĩnh Lính Đánh Thuê]</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Cánh Tay Cơ Khí [Nhà Nghiên Cứu Chính]</t>
+          <t>Cánh Tay Cơ Khí [Trưởng Điều Tra]</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Người Theo Đuổi Phép Màu [Nhân Viên Quay Phim]</t>
+          <t>Người Đàn Ông Theo Đuổi Phép Màu [Nhân Viên Quay Phim]</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Người Ngưỡng Mộ Phép Màu [Biên Tập Viên Phim]</t>
+          <t>Người Đàn Ông Kinh Ngạc Trước Phép Màu [Biên Tập Viên Phim]</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Worried Tour Guide [Lighting Technician]</t>
+          <t>Hướng Dẫn Viên Lo Lắng [Kỹ Thuật Chiếu Sáng]</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Meticulous Traveler [Film Producer]</t>
+          <t>Nhà Sản Xuất Phim Tỉ Mỉ [Meticulous Traveler]</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Curious Traveler [Makeup Designer]</t>
+          <t>Lữ Khách Tò Mò [Thiết Kế Trang Điểm]</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Lữ Khách Đội Mũ Beret [D]</t>
+          <t>Lữ Khách Đội Mũ Nồi [D]</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Hopeless Gambler [Armed Robber]</t>
+          <t>Tay Đánh Bạc Tuyệt Vọng [Tên Cướp Có Vũ Khí]</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Bắt đầu trận đấu</t>
+          <t>Bắt đầu trận chiến</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Bắt đầu trận đấu</t>
+          <t>Bắt đầu trận chiến</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Lose 200 Dream Fragments</t>
+          <t>Mất 200 Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Dùng 50 Mảnh Giấc Mơ để chọn một Phép Ẩn Dụ</t>
+          <t>Dùng 50 Mảnh Giấc Mơ để chọn một Ẩn Dụ.</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Discount Bread</t>
+          <t>Bánh mì giảm giá</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Celebrity-Endorsed Potato Chips</t>
+          <t>Khoai Tây Chiên Được Ngôi Sao Tán Dương</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Nước ngọt có nắp chai trúng thưởng</t>
+          <t>Nước Soda Có Nắp Chai May Mắn</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Tránh rắc rối không cần thiết</t>
+          <t>Tránh gây rắc rối không cần thiết</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>The Alarm</t>
+          <t>Báo Động</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Chiến đấu với [Tethys: Torrent Prescient]</t>
+          <t>Đối đầu [Tethys: Dòng Chảy Tiên Tri]</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Bắt đầu trận chiến cuối và đối mặt [Psyche Pass]</t>
+          <t>Bắt đầu trận chiến cuối cùng và đối mặt với [Psyche Pass]</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Chiến đấu với [Frozen Time]</t>
+          <t>Đối đầu [Thời Gian Đông Cứng]</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Bắt đầu trận chiến cuối và quyết định số phận của cô ấy</t>
+          <t>Bắt đầu trận chiến cuối cùng và quyết định số phận của cô ấy</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Chiến thắng trận chiến khó khăn để nhận 200 Mảnh Giấc Mơ</t>
+          <t>Chiến thắng trận chiến khó để nhận 200 Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Camellya đã tham gia đội của bạn</t>
+          <t>Camellya đã gia nhập đội của bạn</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Aalto đã tham gia đội của bạn</t>
+          <t>Aalto gia nhập đội của bạn</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Nhân viên văn phòng quá sức [Nhân viên ngân hàng]</t>
+          <t>Nhân Viên Văn Phòng Quá Sức [Nhân Viên Ngân Hàng]</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Anh hùng trên cột buồm [Thuyền trưởng Dao Găm Bay]</t>
+          <t>Anh Hùng Trên Cột Buồm [Thuyền Trưởng Phi Đao]</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Cô gái mang hộp đạo cụ [Ảo thuật gia sân khấu]</t>
+          <t>Cô gái khiêng hộp đạo cụ [Ảo thuật gia sân khấu]</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Cô gái tóc vàng óng [Sĩ quan giao thức]</t>
+          <t>Cô Gái Tóc Vàng Lấp Lánh [Sĩ Quan Giao Thức]</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Nhân viên tuần tra buồn ngủ [Lính gác trực]</t>
+          <t>Tuần Tra Mệt Mỏi [Nhiệm Vụ Canh Gác]</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Nhân viên trực ban [Thư ký]</t>
+          <t>Nhân Viên Trực [Thư Ký]</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>White-Robed High Adjudicator [Fenrico]</t>
+          <t>Đại Thẩm Phán Áo Trắng [Fenrico]</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Excited Crowd [Ragunna Citizens]</t>
+          <t>Tuyệt quá! Tuyệt quá!</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Fenrico của biển cả [Người đứng đầu đoàn xiếc]</t>
+          <t>Fenrico của Biển [Người Dẫn Dắt Đoàn Xiếc]</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Nhân viên tuần tra thờ ơ [Sĩ quan an ninh trưởng]</t>
+          <t>Tuần Tra Lãnh Đạm [Chỉ Huy An Ninh]</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Nhân viên tuần tra thờ ơ [Sĩ quan an ninh]</t>
+          <t>Tuần Tra Lãnh Đạm [Nhân Viên An Ninh]</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Cô gái tóc đỏ yêu kiều [Nghệ sĩ dương cầm biển]</t>
+          <t>Cô Gái Tóc Đỏ Như Tiên [Nghệ Sĩ Piano Biển]</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Người phụ nữ đến từ biển sâu [Chủ tịch ngân hàng Current]</t>
+          <t>Người Phụ Nữ Biển Sâu [Chủ tịch Ngân hàng Hiện tại]</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Cô gái tỏa sáng như ngọc opal [Tân trưởng gia tộc]</t>
+          <t>Cô gái lấp lánh như ngọc opan [Tân Gia Chủ]</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Thương nhân nghiêm túc [Nhà thiết kế trang điểm]</t>
+          <t>Thương Nhân Chuyên Nghiệp [Chuyên Gia Trang Điểm]</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Thương nhân kỳ lạ [Diễn viên đóng thế]</t>
+          <t>Thương Nhân Kỳ Lạ [Diễn Viên Đóng Thế]</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Người Đàn Ông Tức Giận [Fallen Knight]</t>
+          <t>Người Đàn Ông Giận Dữ [Hiệp Sĩ Sa Ngã]</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Obedient Youth [Attendant Knight]</t>
+          <t>Thanh Niên Ngoan Hiền [Hộ Vệ Hiệp Sĩ]</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Kẻ Đàn Ông Tàn Nhẫn [Fjord Leader]</t>
+          <t>Kẻ Tàn Nhẫn [Thủ Lĩnh Fjord]</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Surprised Sidekick [Scavenger]</t>
+          <t>Trợ thủ [Scavenger] ngạc nhiên</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Excited Sidekick [Strong Thug]</t>
+          <t>Đồng đội hào hứng [Kẻ du côn lực lưỡng]</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Enthusiastic Auctioneer [Camera Operator]</t>
+          <t>Người Điều Phối Máy Quay nhiệt tình</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Nosy Buyer [Lighting Technician]</t>
+          <t>Khách Hàng Tò Mò [Kỹ Thuật Ánh Sáng]</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Cautious Bidder [Film Producer]</t>
+          <t>Nhà Đầu Tư Thận Trọng [Nhà Sản Xuất Phim]</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Onlookers</t>
+          <t>Khán giả</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Quiet Buyer [Film Editor]</t>
+          <t>Khách Hàng Lặng Lẽ [Biên Tập Phim]</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Determined Buyer [Film Producer]</t>
+          <t>Người mua đã xác định [Nhà sản xuất phim]</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Nhận đạo cụ ma thuật</t>
+          <t>Cầm lấy đạo cụ ma thuật này</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Phoebe đã gia nhập đội của bạn</t>
+          <t>Phoebe đã gia nhập đội của bạn.</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Mở Cửa Hàng Tuyển Dụng với giảm giá thông thường</t>
+          <t>Mở Cửa Hàng Tuyển Dụng với ưu đãi thông thường</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Mở Cửa Hàng Tuyển Dụng với giảm giá "bất ngờ"</t>
+          <t>Mở Cửa Hàng Tuyển Dụng với ưu đãi "bất ngờ"</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Tiêu 400 Mảnh Giấc Mơ để nhận 2 Ẩn Dụ</t>
+          <t>Dùng 400 Mảnh Giấc Mơ để nhận 2 Ẩn Dụ</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Tiêu 100 Mảnh Giấc Mơ để nhận ngẫu nhiên 0-500 Mảnh Giấc Mơ</t>
+          <t>Dùng 100 Mảnh Giấc Mơ để nhận ngẫu nhiên 0-500 Mảnh Giấc Mơ.</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Tiêu 200 Mảnh Giấc Mơ để mở Cửa Hàng Tăng Cường Resonator</t>
+          <t>Dùng 200 Mảnh Giấc Mơ để mở Cửa Hàng Tăng Cường Resonator</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Polished Gentleman [Film Producer]</t>
+          <t>Quý Ông Lịch Lãm [Nhà Sản Xuất Phim]</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Stunt Beauty [Stunt Double]</t>
+          <t>Diễn Viên Đổi Công [Diễn Viên Đóng Thế]</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Daily-Life Vlogger [Camera Operator]</t>
+          <t>Vlogger Cuộc Sống Hằng Ngày [Quay Phim]</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Scarlet Writing [First Puzzle]</t>
+          <t>Chữ Scarlet [Bài Toán Đầu Tiên]</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Tất cả-Around Decorator [Lighting Technician]</t>
+          <t>Chuyên Gia Trang Trí Đa Năng [Kỹ Thuật Chiếu Sáng]</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Thời Thượng [Makeup Designer]</t>
+          <t>Nhà Nghiên Cứu Thời Thượng [Chuyên Gia Trang Điểm]</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Chàng Trai Thông Minh [Famous Director]</t>
+          <t>Bậc Thầy Kính Lúp [Đạo Diễn Nổi Tiếng]</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Beret-Capped Detective [D]</t>
+          <t>Thám Tử Mũ Nồi [D]</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Đứa Trẻ Ít Nói [Film Editor]</t>
+          <t>Đứa Trẻ Lặng Lẽ [Biên Tập Phim]</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Polished Gentleman [Film Producer]</t>
+          <t>Quý Ông Lịch Lãm [Nhà Sản Xuất Phim]</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Lời Tường Thuật Trong Bóng Tối [Giọng nói of Somnoire]</t>
+          <t>Lời Tự Sự Trong Bóng Tối [Giọng Somnoire]</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Nghi Phạm Giết Người [Famous Director]</t>
+          <t>Nghi phạm Giết người [Đạo diễn Nổi tiếng]</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Ánh Nhìn Từ Hư Vô [The White Tower]</t>
+          <t>Ánh Nhìn Từ Tận Cùng [Tháp Trắng]</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Weary Foreseer [Film Producer]</t>
+          <t>Nhà Tiên Tri Mệt Mỏi [Nhà Sản Xuất Phim]</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Nghiêm Túc [Makeup Designer]</t>
+          <t>Nhà Nghiên Cứu Nghiêm Túc [Nhà Thiết Kế Trang Điểm]</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Quản Lý Nghiêm Túc [Famous Director]</t>
+          <t>Quản Lý Nghiêm Túc [Đạo Diễn Nổi Tiếng]</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Đam Mê [Camera Operator]</t>
+          <t>Nhà Nghiên Cứu Nhiệt Huyết [Người Vận Hành Máy Quay]</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Sinh Viên Khoa Nhân Văn Lười Biếng [Stunt Double]</t>
+          <t>Sinh Viên Nhân Văn Lười Biếng [Diễn Viên Đóng Thế]</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Sinh Viên Khoa Khoa Học Tỉ Mỉ [Makeup Designer]</t>
+          <t>Học Sinh Khoa Học Tỉ Mỉ [Thiết Kế Trang Điểm]</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Người Đàn Ông Trong Bộ Đồ Vũ Trụ [Famous Director]</t>
+          <t>Người Đàn Ông Bộ Đồ Vũ Trụ [Đạo Diễn Nổi Tiếng]</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Ground Control's Response [Film Editor]</t>
+          <t>Phản hồi từ Bộ phận Điều khiển Mặt đất [Biên tập phim]</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Cô gái trong bộ đồng phục học sinh [D]</t>
+          <t>Cô gái mặc đồng phục học sinh [D]</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Nhân viên văn phòng ngoài giờ [Diễn viên đóng thế]</t>
+          <t>Nhân Viên Văn Phòng Giờ Tan Tầm [Diễn Viên Đóng Thế]</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Tumbleyak tĩnh lặng [Giọng nói of Somnoire]</t>
+          <t>Một Chú Yak Đang Thiu Thiu [Giọng Somnoire]</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Trưởng lão đáng kính [Nhà sản xuất phim]</t>
+          <t>Trưởng Lão Đáng Kính [Nhà Sản Xuất Phim]</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Cô gái thiên tài cứng đầu [Nhà thiết kế trang điểm]</t>
+          <t>Thiên Tài Cưỡng Chế [Nhà Thiết Kế Trang Điểm]</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Chàng trai quê bướng bỉnh [Nhân viên quay phim]</t>
+          <t>Chàng Trai Quê Bướng Bỉnh [Nhân Viên Quay Phim]</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Chủ cửa hàng xổ số [Kỹ thuật viên ánh sáng]</t>
+          <t>Chủ Cửa Hàng Xổ Số [Kỹ Thuật Viên Ánh Sáng]</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Người đàn ông trung niên thông minh [Đạo diễn nổi tiếng]</t>
+          <t>Quý Ông Trung Niên Thông Thái [Đạo Diễn Nổi Tiếng]</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Quái vật hậu nhân loại [Giọng nói of Somnoire]</t>
+          <t>Quái Vật Hậu Nhân Loại [Giọng Somnoire]</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Titan của Chất Độc [The White Tower]</t>
+          <t>Titan Sinh Độc [Tháp Trắng]</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Cô gái rụt rè [D]</t>
+          <t>Cô Bé Nhút Nhát [D]</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Masked Hero [Stunt Double]</t>
+          <t>Anh Hùng Đeo Mặt Nạ [Diễn Viên Đóng Thế]</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Đặc vụ từ hành tinh khác [Giọng nói of Somnoire]</t>
+          <t>Đặc Vụ Đến Từ Hành Tinh Khác [Giọng Somnoire]</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Chixia đã gia nhập đội của bạn</t>
+          <t>Chixia đã gia nhập đội của bạn.</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Encore và Calcharo đã gia nhập đội của bạn</t>
+          <t>Encore và Calcharo đã gia nhập đội của cậu</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Nhận 100-200 Mảnh Giấc Mơ</t>
+          <t>Thu thập 100-200 Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Mất hoặc nhận được Phim Cuộn: -12-24</t>
+          <t>Mất hoặc nhận Cuộn Phim: -12~24</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Người lái gondola thư thái [Giọng nói of Somnoire]</t>
+          <t>Người Chèo Thuyền Thong Dong [Tiếng Nói Somnoire]</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Vào Carnevale và thu hồi các khoản nợ cũ</t>
+          <t>Bước vào Carnevale và đòi lại những món nợ cũ.</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Đối mặt với cơn ác mộng từ sâu thẳm Somnoire</t>
+          <t>Đối mặt với cơn ác mộng từ vực sâu Somnoire</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Nhận lời chúc phúc từ Chúa tể Somnoire</t>
+          <t>Nhận lời chúc phúc từ Lãnh Chúa Somnoire</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Respite Event</t>
+          <t>Sự Kiện Nghỉ Dưỡng</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Jinhsi đã gia nhập đội của bạn</t>
+          <t>Jinhsi đã tham gia đội của bạn</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Changli và Sanhua đã tham gia đội của bạn</t>
+          <t>Changli và Sanhua đã tham gia đội của cậu</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Gặp gỡ: Vấp ngã trên chuyến tàu bỏ hoang III</t>
+          <t>Gặp gỡ: Chuyến Tàu Bỏ Hoang III</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Nhận 120 Mảnh Giấc Mơ</t>
+          <t>Thu thập 120 Mảnh Giấc Mơ.</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Lose 50 Dream Fragments</t>
+          <t>Mất 50 Mảnh Giấc Mơ</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Hoàn thành "Chương Chính: Đền Thờ" để mở khóa</t>
+          <t>Hoàn thành "Main Story: Temple" để mở khóa</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Hoàn thành "Chương Chính: Đoàn Tụ" để mở khóa</t>
+          <t>Hoàn thành "Main Story: Reunion" để mở khóa</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Hoàn thành "Chương Chính: Người Môi Giới Thông Tin" để mở khóa</t>
+          <t>Hoàn thành "Main Story: Information Broker" để mở khóa</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi Shorekeeper tham gia đội</t>
+          <t>Mở khóa sau khi Shorekeeper gia nhập đội.</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
